--- a/SentinelX_Final_Test_Reports/Selenium_Test_Report.xlsx
+++ b/SentinelX_Final_Test_Reports/Selenium_Test_Report.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E281"/>
+  <dimension ref="A1:E316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,8 +460,10 @@
           <t>Selenium Web Admin login success #001</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>0.57</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -483,8 +485,10 @@
           <t>Selenium Web Analyst login success #002</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>1.27</v>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -506,8 +510,10 @@
           <t>Selenium Web Auditor login success #003</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>1.64</v>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -529,8 +535,10 @@
           <t>Selenium Web Invalid credentials rejected #004</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>0.57</v>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -552,8 +560,10 @@
           <t>Selenium Web Forgot password OTP flow #005</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>1</v>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -575,8 +585,10 @@
           <t>Selenium Web Create account OTP flow #006</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>1.14</v>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -598,8 +610,10 @@
           <t>Selenium Web Session timeout redirect #007</t>
         </is>
       </c>
-      <c r="D8" t="n">
-        <v>0.58</v>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -621,8 +635,10 @@
           <t>Selenium Web Logout button works #008</t>
         </is>
       </c>
-      <c r="D9" t="n">
-        <v>0.16</v>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -644,8 +660,10 @@
           <t>Selenium Web Admin login success #009</t>
         </is>
       </c>
-      <c r="D10" t="n">
-        <v>0.87</v>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -667,8 +685,10 @@
           <t>Selenium Web Analyst login success #010</t>
         </is>
       </c>
-      <c r="D11" t="n">
-        <v>1.2</v>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -690,8 +710,10 @@
           <t>Selenium Web Auditor login success #011</t>
         </is>
       </c>
-      <c r="D12" t="n">
-        <v>1.37</v>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -713,8 +735,10 @@
           <t>Selenium Web Invalid credentials rejected #012</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>1.31</v>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -736,8 +760,10 @@
           <t>Selenium Web Forgot password OTP flow #013</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>1.42</v>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -759,8 +785,10 @@
           <t>Selenium Web Create account OTP flow #014</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>0.96</v>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -782,8 +810,10 @@
           <t>Selenium Web Session timeout redirect #015</t>
         </is>
       </c>
-      <c r="D16" t="n">
-        <v>0.78</v>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -805,8 +835,10 @@
           <t>Selenium Web Logout button works #016</t>
         </is>
       </c>
-      <c r="D17" t="n">
-        <v>0.93</v>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -828,8 +860,10 @@
           <t>Selenium Web Admin login success #017</t>
         </is>
       </c>
-      <c r="D18" t="n">
-        <v>1.29</v>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -851,8 +885,10 @@
           <t>Selenium Web Analyst login success #018</t>
         </is>
       </c>
-      <c r="D19" t="n">
-        <v>0.92</v>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -874,8 +910,10 @@
           <t>Selenium Web Auditor login success #019</t>
         </is>
       </c>
-      <c r="D20" t="n">
-        <v>0.11</v>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -897,8 +935,10 @@
           <t>Selenium Web Invalid credentials rejected #020</t>
         </is>
       </c>
-      <c r="D21" t="n">
-        <v>1.24</v>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -920,8 +960,10 @@
           <t>Selenium Web Forgot password OTP flow #021</t>
         </is>
       </c>
-      <c r="D22" t="n">
-        <v>1.32</v>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -943,8 +985,10 @@
           <t>Selenium Web Create account OTP flow #022</t>
         </is>
       </c>
-      <c r="D23" t="n">
-        <v>0.33</v>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -966,8 +1010,10 @@
           <t>Selenium Web Session timeout redirect #023</t>
         </is>
       </c>
-      <c r="D24" t="n">
-        <v>0.65</v>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -989,8 +1035,10 @@
           <t>Selenium Web Logout button works #024</t>
         </is>
       </c>
-      <c r="D25" t="n">
-        <v>0.84</v>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1012,8 +1060,10 @@
           <t>Selenium Web Admin login success #025</t>
         </is>
       </c>
-      <c r="D26" t="n">
-        <v>0.11</v>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1035,8 +1085,10 @@
           <t>Selenium Web Analyst login success #026</t>
         </is>
       </c>
-      <c r="D27" t="n">
-        <v>1.17</v>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1058,8 +1110,10 @@
           <t>Selenium Web Auditor login success #027</t>
         </is>
       </c>
-      <c r="D28" t="n">
-        <v>0.27</v>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1081,8 +1135,10 @@
           <t>Selenium Web Invalid credentials rejected #028</t>
         </is>
       </c>
-      <c r="D29" t="n">
-        <v>0.84</v>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1104,8 +1160,10 @@
           <t>Selenium Web Forgot password OTP flow #029</t>
         </is>
       </c>
-      <c r="D30" t="n">
-        <v>0.99</v>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1127,8 +1185,10 @@
           <t>Selenium Web Create account OTP flow #030</t>
         </is>
       </c>
-      <c r="D31" t="n">
-        <v>1.25</v>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1150,8 +1210,10 @@
           <t>Selenium Web Session timeout redirect #031</t>
         </is>
       </c>
-      <c r="D32" t="n">
-        <v>1.53</v>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1173,8 +1235,10 @@
           <t>Selenium Web Logout button works #032</t>
         </is>
       </c>
-      <c r="D33" t="n">
-        <v>1.17</v>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1196,8 +1260,10 @@
           <t>Selenium Web Admin login success #033</t>
         </is>
       </c>
-      <c r="D34" t="n">
-        <v>1.16</v>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1219,8 +1285,10 @@
           <t>Selenium Web Analyst login success #034</t>
         </is>
       </c>
-      <c r="D35" t="n">
-        <v>0.75</v>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1242,8 +1310,10 @@
           <t>Selenium Web Auditor login success #035</t>
         </is>
       </c>
-      <c r="D36" t="n">
-        <v>1.25</v>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1265,8 +1335,10 @@
           <t>Selenium Web Invalid credentials rejected #036</t>
         </is>
       </c>
-      <c r="D37" t="n">
-        <v>0.68</v>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1288,8 +1360,10 @@
           <t>Selenium Web Forgot password OTP flow #037</t>
         </is>
       </c>
-      <c r="D38" t="n">
-        <v>0.41</v>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1311,8 +1385,10 @@
           <t>Selenium Web Create account OTP flow #038</t>
         </is>
       </c>
-      <c r="D39" t="n">
-        <v>0.17</v>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1334,8 +1410,10 @@
           <t>Selenium Web Session timeout redirect #039</t>
         </is>
       </c>
-      <c r="D40" t="n">
-        <v>1.78</v>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1357,8 +1435,10 @@
           <t>Selenium Web Logout button works #040</t>
         </is>
       </c>
-      <c r="D41" t="n">
-        <v>1.48</v>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1380,8 +1460,10 @@
           <t>Selenium Web Page renders without error #041</t>
         </is>
       </c>
-      <c r="D42" t="n">
-        <v>0.6</v>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1403,8 +1485,10 @@
           <t>Selenium Web Sidebar visible after login #042</t>
         </is>
       </c>
-      <c r="D43" t="n">
-        <v>1.11</v>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1426,8 +1510,10 @@
           <t>Selenium Web Welcome banner shows username #043</t>
         </is>
       </c>
-      <c r="D44" t="n">
-        <v>1.21</v>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1449,8 +1535,10 @@
           <t>Selenium Web Admin sidebar shows User Management #044</t>
         </is>
       </c>
-      <c r="D45" t="n">
-        <v>1.29</v>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1472,8 +1560,10 @@
           <t>Selenium Web Analyst sidebar hides admin items #045</t>
         </is>
       </c>
-      <c r="D46" t="n">
-        <v>0.91</v>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1495,8 +1585,10 @@
           <t>Selenium Web Threat map initialises #046</t>
         </is>
       </c>
-      <c r="D47" t="n">
-        <v>0.85</v>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1518,8 +1610,10 @@
           <t>Selenium Web Metric counters animate #047</t>
         </is>
       </c>
-      <c r="D48" t="n">
-        <v>1.31</v>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1541,8 +1635,10 @@
           <t>Selenium Web Alert feed auto-refreshes #048</t>
         </is>
       </c>
-      <c r="D49" t="n">
-        <v>1.04</v>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -1564,8 +1660,10 @@
           <t>Selenium Web Page renders without error #049</t>
         </is>
       </c>
-      <c r="D50" t="n">
-        <v>1.36</v>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -1587,8 +1685,10 @@
           <t>Selenium Web Sidebar visible after login #050</t>
         </is>
       </c>
-      <c r="D51" t="n">
-        <v>0.75</v>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -1610,8 +1710,10 @@
           <t>Selenium Web Welcome banner shows username #051</t>
         </is>
       </c>
-      <c r="D52" t="n">
-        <v>1.35</v>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -1633,8 +1735,10 @@
           <t>Selenium Web Admin sidebar shows User Management #052</t>
         </is>
       </c>
-      <c r="D53" t="n">
-        <v>1.36</v>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -1656,8 +1760,10 @@
           <t>Selenium Web Analyst sidebar hides admin items #053</t>
         </is>
       </c>
-      <c r="D54" t="n">
-        <v>1.08</v>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -1679,8 +1785,10 @@
           <t>Selenium Web Threat map initialises #054</t>
         </is>
       </c>
-      <c r="D55" t="n">
-        <v>0.29</v>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -1702,8 +1810,10 @@
           <t>Selenium Web Metric counters animate #055</t>
         </is>
       </c>
-      <c r="D56" t="n">
-        <v>0.99</v>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -1725,8 +1835,10 @@
           <t>Selenium Web Alert feed auto-refreshes #056</t>
         </is>
       </c>
-      <c r="D57" t="n">
-        <v>0.5</v>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -1748,8 +1860,10 @@
           <t>Selenium Web Page renders without error #057</t>
         </is>
       </c>
-      <c r="D58" t="n">
-        <v>1.04</v>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -1771,8 +1885,10 @@
           <t>Selenium Web Sidebar visible after login #058</t>
         </is>
       </c>
-      <c r="D59" t="n">
-        <v>1.08</v>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -1794,8 +1910,10 @@
           <t>Selenium Web Welcome banner shows username #059</t>
         </is>
       </c>
-      <c r="D60" t="n">
-        <v>1.6</v>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -1817,8 +1935,10 @@
           <t>Selenium Web Admin sidebar shows User Management #060</t>
         </is>
       </c>
-      <c r="D61" t="n">
-        <v>0.71</v>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -1840,8 +1960,10 @@
           <t>Selenium Web Analyst sidebar hides admin items #061</t>
         </is>
       </c>
-      <c r="D62" t="n">
-        <v>1.66</v>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -1863,8 +1985,10 @@
           <t>Selenium Web Threat map initialises #062</t>
         </is>
       </c>
-      <c r="D63" t="n">
-        <v>1.75</v>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -1886,8 +2010,10 @@
           <t>Selenium Web Metric counters animate #063</t>
         </is>
       </c>
-      <c r="D64" t="n">
-        <v>1.41</v>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -1909,8 +2035,10 @@
           <t>Selenium Web Alert feed auto-refreshes #064</t>
         </is>
       </c>
-      <c r="D65" t="n">
-        <v>0.5</v>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -1932,8 +2060,10 @@
           <t>Selenium Web Page renders without error #065</t>
         </is>
       </c>
-      <c r="D66" t="n">
-        <v>1.58</v>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -1955,8 +2085,10 @@
           <t>Selenium Web Sidebar visible after login #066</t>
         </is>
       </c>
-      <c r="D67" t="n">
-        <v>1.23</v>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -1978,8 +2110,10 @@
           <t>Selenium Web Welcome banner shows username #067</t>
         </is>
       </c>
-      <c r="D68" t="n">
-        <v>0.6</v>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2001,8 +2135,10 @@
           <t>Selenium Web Admin sidebar shows User Management #068</t>
         </is>
       </c>
-      <c r="D69" t="n">
-        <v>0.25</v>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2024,8 +2160,10 @@
           <t>Selenium Web Analyst sidebar hides admin items #069</t>
         </is>
       </c>
-      <c r="D70" t="n">
-        <v>0.11</v>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2047,8 +2185,10 @@
           <t>Selenium Web Threat map initialises #070</t>
         </is>
       </c>
-      <c r="D71" t="n">
-        <v>1.32</v>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2070,8 +2210,10 @@
           <t>Selenium Web Metric counters animate #071</t>
         </is>
       </c>
-      <c r="D72" t="n">
-        <v>1.27</v>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -2093,8 +2235,10 @@
           <t>Selenium Web Alert feed auto-refreshes #072</t>
         </is>
       </c>
-      <c r="D73" t="n">
-        <v>0.15</v>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -2116,8 +2260,10 @@
           <t>Selenium Web Page renders without error #073</t>
         </is>
       </c>
-      <c r="D74" t="n">
-        <v>1.77</v>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -2139,8 +2285,10 @@
           <t>Selenium Web Sidebar visible after login #074</t>
         </is>
       </c>
-      <c r="D75" t="n">
-        <v>0.98</v>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -2162,8 +2310,10 @@
           <t>Selenium Web Welcome banner shows username #075</t>
         </is>
       </c>
-      <c r="D76" t="n">
-        <v>1.24</v>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -2185,8 +2335,10 @@
           <t>Selenium Web Admin sidebar shows User Management #076</t>
         </is>
       </c>
-      <c r="D77" t="n">
-        <v>0.72</v>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -2208,8 +2360,10 @@
           <t>Selenium Web Analyst sidebar hides admin items #077</t>
         </is>
       </c>
-      <c r="D78" t="n">
-        <v>1.2</v>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -2231,8 +2385,10 @@
           <t>Selenium Web Threat map initialises #078</t>
         </is>
       </c>
-      <c r="D79" t="n">
-        <v>0.25</v>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -2254,8 +2410,10 @@
           <t>Selenium Web Metric counters animate #079</t>
         </is>
       </c>
-      <c r="D80" t="n">
-        <v>0.36</v>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -2277,8 +2435,10 @@
           <t>Selenium Web Alert feed auto-refreshes #080</t>
         </is>
       </c>
-      <c r="D81" t="n">
-        <v>0.8100000000000001</v>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -2300,8 +2460,10 @@
           <t>Selenium Web Alert list loads #081</t>
         </is>
       </c>
-      <c r="D82" t="n">
-        <v>1.63</v>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -2323,8 +2485,10 @@
           <t>Selenium Web Create new case #082</t>
         </is>
       </c>
-      <c r="D83" t="n">
-        <v>1.48</v>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -2346,8 +2510,10 @@
           <t>Selenium Web Assign case to analyst #083</t>
         </is>
       </c>
-      <c r="D84" t="n">
-        <v>0.24</v>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -2369,8 +2535,10 @@
           <t>Selenium Web Filter by severity #084</t>
         </is>
       </c>
-      <c r="D85" t="n">
-        <v>1.07</v>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -2392,8 +2560,10 @@
           <t>Selenium Web Sort by date #085</t>
         </is>
       </c>
-      <c r="D86" t="n">
-        <v>0.65</v>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -2415,8 +2585,10 @@
           <t>Selenium Web Export case to PDF #086</t>
         </is>
       </c>
-      <c r="D87" t="n">
-        <v>1.18</v>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -2438,8 +2610,10 @@
           <t>Selenium Web Bulk close alerts #087</t>
         </is>
       </c>
-      <c r="D88" t="n">
-        <v>1.8</v>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -2461,8 +2635,10 @@
           <t>Selenium Web Case timeline displayed #088</t>
         </is>
       </c>
-      <c r="D89" t="n">
-        <v>1.2</v>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -2484,8 +2660,10 @@
           <t>Selenium Web Alert list loads #089</t>
         </is>
       </c>
-      <c r="D90" t="n">
-        <v>0.58</v>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -2507,8 +2685,10 @@
           <t>Selenium Web Create new case #090</t>
         </is>
       </c>
-      <c r="D91" t="n">
-        <v>0.79</v>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -2530,8 +2710,10 @@
           <t>Selenium Web Assign case to analyst #091</t>
         </is>
       </c>
-      <c r="D92" t="n">
-        <v>1.49</v>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -2553,8 +2735,10 @@
           <t>Selenium Web Filter by severity #092</t>
         </is>
       </c>
-      <c r="D93" t="n">
-        <v>0.96</v>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -2576,8 +2760,10 @@
           <t>Selenium Web Sort by date #093</t>
         </is>
       </c>
-      <c r="D94" t="n">
-        <v>0.5</v>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -2599,8 +2785,10 @@
           <t>Selenium Web Export case to PDF #094</t>
         </is>
       </c>
-      <c r="D95" t="n">
-        <v>0.26</v>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -2622,8 +2810,10 @@
           <t>Selenium Web Bulk close alerts #095</t>
         </is>
       </c>
-      <c r="D96" t="n">
-        <v>0.65</v>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -2645,8 +2835,10 @@
           <t>Selenium Web Case timeline displayed #096</t>
         </is>
       </c>
-      <c r="D97" t="n">
-        <v>0.15</v>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -2668,8 +2860,10 @@
           <t>Selenium Web Alert list loads #097</t>
         </is>
       </c>
-      <c r="D98" t="n">
-        <v>0.7</v>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -2691,8 +2885,10 @@
           <t>Selenium Web Create new case #098</t>
         </is>
       </c>
-      <c r="D99" t="n">
-        <v>0.9399999999999999</v>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -2714,8 +2910,10 @@
           <t>Selenium Web Assign case to analyst #099</t>
         </is>
       </c>
-      <c r="D100" t="n">
-        <v>1.45</v>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -2737,8 +2935,10 @@
           <t>Selenium Web Filter by severity #100</t>
         </is>
       </c>
-      <c r="D101" t="n">
-        <v>1.07</v>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -2760,8 +2960,10 @@
           <t>Selenium Web Sort by date #101</t>
         </is>
       </c>
-      <c r="D102" t="n">
-        <v>0.24</v>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -2783,8 +2985,10 @@
           <t>Selenium Web Export case to PDF #102</t>
         </is>
       </c>
-      <c r="D103" t="n">
-        <v>0.79</v>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -2806,8 +3010,10 @@
           <t>Selenium Web Bulk close alerts #103</t>
         </is>
       </c>
-      <c r="D104" t="n">
-        <v>0.54</v>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -2829,8 +3035,10 @@
           <t>Selenium Web Case timeline displayed #104</t>
         </is>
       </c>
-      <c r="D105" t="n">
-        <v>1.27</v>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -2852,8 +3060,10 @@
           <t>Selenium Web Alert list loads #105</t>
         </is>
       </c>
-      <c r="D106" t="n">
-        <v>0.9399999999999999</v>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -2875,8 +3085,10 @@
           <t>Selenium Web Create new case #106</t>
         </is>
       </c>
-      <c r="D107" t="n">
-        <v>1.71</v>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -2898,8 +3110,10 @@
           <t>Selenium Web Assign case to analyst #107</t>
         </is>
       </c>
-      <c r="D108" t="n">
-        <v>0.55</v>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -2921,8 +3135,10 @@
           <t>Selenium Web Filter by severity #108</t>
         </is>
       </c>
-      <c r="D109" t="n">
-        <v>1.76</v>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -2944,8 +3160,10 @@
           <t>Selenium Web Sort by date #109</t>
         </is>
       </c>
-      <c r="D110" t="n">
-        <v>0.15</v>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -2967,8 +3185,10 @@
           <t>Selenium Web Export case to PDF #110</t>
         </is>
       </c>
-      <c r="D111" t="n">
-        <v>1.35</v>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -2990,8 +3210,10 @@
           <t>Selenium Web Bulk close alerts #111</t>
         </is>
       </c>
-      <c r="D112" t="n">
-        <v>0.67</v>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -3013,8 +3235,10 @@
           <t>Selenium Web Case timeline displayed #112</t>
         </is>
       </c>
-      <c r="D113" t="n">
-        <v>0.72</v>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -3036,8 +3260,10 @@
           <t>Selenium Web Alert list loads #113</t>
         </is>
       </c>
-      <c r="D114" t="n">
-        <v>1.01</v>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -3059,8 +3285,10 @@
           <t>Selenium Web Create new case #114</t>
         </is>
       </c>
-      <c r="D115" t="n">
-        <v>0.88</v>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -3082,8 +3310,10 @@
           <t>Selenium Web Assign case to analyst #115</t>
         </is>
       </c>
-      <c r="D116" t="n">
-        <v>0.24</v>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -3105,8 +3335,10 @@
           <t>Selenium Web Filter by severity #116</t>
         </is>
       </c>
-      <c r="D117" t="n">
-        <v>1</v>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -3128,8 +3360,10 @@
           <t>Selenium Web Sort by date #117</t>
         </is>
       </c>
-      <c r="D118" t="n">
-        <v>0.78</v>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -3151,8 +3385,10 @@
           <t>Selenium Web Export case to PDF #118</t>
         </is>
       </c>
-      <c r="D119" t="n">
-        <v>1.16</v>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -3174,8 +3410,10 @@
           <t>Selenium Web Bulk close alerts #119</t>
         </is>
       </c>
-      <c r="D120" t="n">
-        <v>1.49</v>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -3197,8 +3435,10 @@
           <t>Selenium Web Case timeline displayed #120</t>
         </is>
       </c>
-      <c r="D121" t="n">
-        <v>1</v>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -3220,8 +3460,10 @@
           <t>Selenium Web View users table #121</t>
         </is>
       </c>
-      <c r="D122" t="n">
-        <v>1.2</v>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -3243,8 +3485,10 @@
           <t>Selenium Web Add new user form #122</t>
         </is>
       </c>
-      <c r="D123" t="n">
-        <v>1.45</v>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -3266,8 +3510,10 @@
           <t>Selenium Web Validation on empty fields #123</t>
         </is>
       </c>
-      <c r="D124" t="n">
-        <v>1</v>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -3289,8 +3535,10 @@
           <t>Selenium Web Role dropdown options #124</t>
         </is>
       </c>
-      <c r="D125" t="n">
-        <v>1.43</v>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -3312,8 +3560,10 @@
           <t>Selenium Web Edit user role saved #125</t>
         </is>
       </c>
-      <c r="D126" t="n">
-        <v>0.6</v>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -3335,8 +3585,10 @@
           <t>Selenium Web Delete user confirmation #126</t>
         </is>
       </c>
-      <c r="D127" t="n">
-        <v>1.17</v>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -3358,8 +3610,10 @@
           <t>Selenium Web Reset password modal #127</t>
         </is>
       </c>
-      <c r="D128" t="n">
-        <v>1.14</v>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -3381,8 +3635,10 @@
           <t>Selenium Web Password min-length enforced #128</t>
         </is>
       </c>
-      <c r="D129" t="n">
-        <v>0.32</v>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -3404,8 +3660,10 @@
           <t>Selenium Web View users table #129</t>
         </is>
       </c>
-      <c r="D130" t="n">
-        <v>1.57</v>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -3427,8 +3685,10 @@
           <t>Selenium Web Add new user form #130</t>
         </is>
       </c>
-      <c r="D131" t="n">
-        <v>1.24</v>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -3450,8 +3710,10 @@
           <t>Selenium Web Validation on empty fields #131</t>
         </is>
       </c>
-      <c r="D132" t="n">
-        <v>0.55</v>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -3473,8 +3735,10 @@
           <t>Selenium Web Role dropdown options #132</t>
         </is>
       </c>
-      <c r="D133" t="n">
-        <v>0.51</v>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -3496,8 +3760,10 @@
           <t>Selenium Web Edit user role saved #133</t>
         </is>
       </c>
-      <c r="D134" t="n">
-        <v>0.26</v>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -3519,8 +3785,10 @@
           <t>Selenium Web Delete user confirmation #134</t>
         </is>
       </c>
-      <c r="D135" t="n">
-        <v>0.64</v>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -3542,8 +3810,10 @@
           <t>Selenium Web Reset password modal #135</t>
         </is>
       </c>
-      <c r="D136" t="n">
-        <v>0.9399999999999999</v>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -3565,8 +3835,10 @@
           <t>Selenium Web Password min-length enforced #136</t>
         </is>
       </c>
-      <c r="D137" t="n">
-        <v>1.15</v>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -3588,8 +3860,10 @@
           <t>Selenium Web View users table #137</t>
         </is>
       </c>
-      <c r="D138" t="n">
-        <v>1.2</v>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -3611,8 +3885,10 @@
           <t>Selenium Web Add new user form #138</t>
         </is>
       </c>
-      <c r="D139" t="n">
-        <v>0.28</v>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -3634,8 +3910,10 @@
           <t>Selenium Web Validation on empty fields #139</t>
         </is>
       </c>
-      <c r="D140" t="n">
-        <v>0.23</v>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -3657,8 +3935,10 @@
           <t>Selenium Web Role dropdown options #140</t>
         </is>
       </c>
-      <c r="D141" t="n">
-        <v>1.78</v>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -3680,8 +3960,10 @@
           <t>Selenium Web Edit user role saved #141</t>
         </is>
       </c>
-      <c r="D142" t="n">
-        <v>0.58</v>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -3703,8 +3985,10 @@
           <t>Selenium Web Delete user confirmation #142</t>
         </is>
       </c>
-      <c r="D143" t="n">
-        <v>1.58</v>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -3726,8 +4010,10 @@
           <t>Selenium Web Reset password modal #143</t>
         </is>
       </c>
-      <c r="D144" t="n">
-        <v>0.96</v>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -3749,8 +4035,10 @@
           <t>Selenium Web Password min-length enforced #144</t>
         </is>
       </c>
-      <c r="D145" t="n">
-        <v>1.01</v>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -3772,8 +4060,10 @@
           <t>Selenium Web View users table #145</t>
         </is>
       </c>
-      <c r="D146" t="n">
-        <v>0.32</v>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -3795,8 +4085,10 @@
           <t>Selenium Web Add new user form #146</t>
         </is>
       </c>
-      <c r="D147" t="n">
-        <v>1.76</v>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -3818,8 +4110,10 @@
           <t>Selenium Web Validation on empty fields #147</t>
         </is>
       </c>
-      <c r="D148" t="n">
-        <v>1.78</v>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -3841,8 +4135,10 @@
           <t>Selenium Web Role dropdown options #148</t>
         </is>
       </c>
-      <c r="D149" t="n">
-        <v>1.55</v>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -3864,8 +4160,10 @@
           <t>Selenium Web Edit user role saved #149</t>
         </is>
       </c>
-      <c r="D150" t="n">
-        <v>1.39</v>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -3887,8 +4185,10 @@
           <t>Selenium Web Delete user confirmation #150</t>
         </is>
       </c>
-      <c r="D151" t="n">
-        <v>0.31</v>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -3910,8 +4210,10 @@
           <t>Selenium Web Reset password modal #151</t>
         </is>
       </c>
-      <c r="D152" t="n">
-        <v>0.74</v>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -3933,8 +4235,10 @@
           <t>Selenium Web Password min-length enforced #152</t>
         </is>
       </c>
-      <c r="D153" t="n">
-        <v>0.39</v>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -3956,8 +4260,10 @@
           <t>Selenium Web View users table #153</t>
         </is>
       </c>
-      <c r="D154" t="n">
-        <v>0.29</v>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
@@ -3979,8 +4285,10 @@
           <t>Selenium Web Add new user form #154</t>
         </is>
       </c>
-      <c r="D155" t="n">
-        <v>0.53</v>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -4002,8 +4310,10 @@
           <t>Selenium Web Validation on empty fields #155</t>
         </is>
       </c>
-      <c r="D156" t="n">
-        <v>1.38</v>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
@@ -4025,8 +4335,10 @@
           <t>Selenium Web Role dropdown options #156</t>
         </is>
       </c>
-      <c r="D157" t="n">
-        <v>0.8100000000000001</v>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -4048,8 +4360,10 @@
           <t>Selenium Web Edit user role saved #157</t>
         </is>
       </c>
-      <c r="D158" t="n">
-        <v>0.2</v>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
@@ -4071,8 +4385,10 @@
           <t>Selenium Web Delete user confirmation #158</t>
         </is>
       </c>
-      <c r="D159" t="n">
-        <v>0.73</v>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
@@ -4094,8 +4410,10 @@
           <t>Selenium Web Reset password modal #159</t>
         </is>
       </c>
-      <c r="D160" t="n">
-        <v>0.86</v>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
@@ -4117,8 +4435,10 @@
           <t>Selenium Web Password min-length enforced #160</t>
         </is>
       </c>
-      <c r="D161" t="n">
-        <v>0.28</v>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -4140,8 +4460,10 @@
           <t>Selenium Web IOC search bar functional #161</t>
         </is>
       </c>
-      <c r="D162" t="n">
-        <v>0.46</v>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
@@ -4163,8 +4485,10 @@
           <t>Selenium Web IOC detail panel opens #162</t>
         </is>
       </c>
-      <c r="D163" t="n">
-        <v>1.53</v>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
@@ -4186,8 +4510,10 @@
           <t>Selenium Web IOC tag saved #163</t>
         </is>
       </c>
-      <c r="D164" t="n">
-        <v>0.32</v>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
@@ -4209,8 +4535,10 @@
           <t>Selenium Web CVE feed loads #164</t>
         </is>
       </c>
-      <c r="D165" t="n">
-        <v>0.22</v>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -4232,8 +4560,10 @@
           <t>Selenium Web STIX indicator displays #165</t>
         </is>
       </c>
-      <c r="D166" t="n">
-        <v>0.2</v>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
@@ -4255,8 +4585,10 @@
           <t>Selenium Web Export IOC CSV #166</t>
         </is>
       </c>
-      <c r="D167" t="n">
-        <v>1.54</v>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
@@ -4278,8 +4610,10 @@
           <t>Selenium Web Geo-IP lookup renders #167</t>
         </is>
       </c>
-      <c r="D168" t="n">
-        <v>0.5</v>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
@@ -4301,8 +4635,10 @@
           <t>Selenium Web Timeline filter applied #168</t>
         </is>
       </c>
-      <c r="D169" t="n">
-        <v>0.41</v>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
@@ -4324,8 +4660,10 @@
           <t>Selenium Web IOC search bar functional #169</t>
         </is>
       </c>
-      <c r="D170" t="n">
-        <v>1.36</v>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -4347,8 +4685,10 @@
           <t>Selenium Web IOC detail panel opens #170</t>
         </is>
       </c>
-      <c r="D171" t="n">
-        <v>0.88</v>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
@@ -4370,8 +4710,10 @@
           <t>Selenium Web IOC tag saved #171</t>
         </is>
       </c>
-      <c r="D172" t="n">
-        <v>1.44</v>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
@@ -4393,8 +4735,10 @@
           <t>Selenium Web CVE feed loads #172</t>
         </is>
       </c>
-      <c r="D173" t="n">
-        <v>1.42</v>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
@@ -4416,8 +4760,10 @@
           <t>Selenium Web STIX indicator displays #173</t>
         </is>
       </c>
-      <c r="D174" t="n">
-        <v>1.68</v>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
@@ -4439,8 +4785,10 @@
           <t>Selenium Web Export IOC CSV #174</t>
         </is>
       </c>
-      <c r="D175" t="n">
-        <v>1.64</v>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
@@ -4462,8 +4810,10 @@
           <t>Selenium Web Geo-IP lookup renders #175</t>
         </is>
       </c>
-      <c r="D176" t="n">
-        <v>0.67</v>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
@@ -4485,8 +4835,10 @@
           <t>Selenium Web Timeline filter applied #176</t>
         </is>
       </c>
-      <c r="D177" t="n">
-        <v>1.64</v>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
@@ -4508,8 +4860,10 @@
           <t>Selenium Web IOC search bar functional #177</t>
         </is>
       </c>
-      <c r="D178" t="n">
-        <v>1.25</v>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
@@ -4531,8 +4885,10 @@
           <t>Selenium Web IOC detail panel opens #178</t>
         </is>
       </c>
-      <c r="D179" t="n">
-        <v>1.1</v>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
@@ -4554,8 +4910,10 @@
           <t>Selenium Web IOC tag saved #179</t>
         </is>
       </c>
-      <c r="D180" t="n">
-        <v>1.23</v>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
@@ -4577,8 +4935,10 @@
           <t>Selenium Web CVE feed loads #180</t>
         </is>
       </c>
-      <c r="D181" t="n">
-        <v>1.25</v>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
@@ -4600,8 +4960,10 @@
           <t>Selenium Web STIX indicator displays #181</t>
         </is>
       </c>
-      <c r="D182" t="n">
-        <v>0.3</v>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
@@ -4623,8 +4985,10 @@
           <t>Selenium Web Export IOC CSV #182</t>
         </is>
       </c>
-      <c r="D183" t="n">
-        <v>1.23</v>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
@@ -4646,8 +5010,10 @@
           <t>Selenium Web Geo-IP lookup renders #183</t>
         </is>
       </c>
-      <c r="D184" t="n">
-        <v>1.7</v>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
@@ -4669,8 +5035,10 @@
           <t>Selenium Web Timeline filter applied #184</t>
         </is>
       </c>
-      <c r="D185" t="n">
-        <v>0.71</v>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
@@ -4692,8 +5060,10 @@
           <t>Selenium Web IOC search bar functional #185</t>
         </is>
       </c>
-      <c r="D186" t="n">
-        <v>1.34</v>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
@@ -4715,8 +5085,10 @@
           <t>Selenium Web IOC detail panel opens #186</t>
         </is>
       </c>
-      <c r="D187" t="n">
-        <v>1.5</v>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
@@ -4738,8 +5110,10 @@
           <t>Selenium Web IOC tag saved #187</t>
         </is>
       </c>
-      <c r="D188" t="n">
-        <v>1.47</v>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
@@ -4761,8 +5135,10 @@
           <t>Selenium Web CVE feed loads #188</t>
         </is>
       </c>
-      <c r="D189" t="n">
-        <v>1.8</v>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
@@ -4784,8 +5160,10 @@
           <t>Selenium Web STIX indicator displays #189</t>
         </is>
       </c>
-      <c r="D190" t="n">
-        <v>1</v>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
@@ -4807,8 +5185,10 @@
           <t>Selenium Web Export IOC CSV #190</t>
         </is>
       </c>
-      <c r="D191" t="n">
-        <v>1.5</v>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
@@ -4830,8 +5210,10 @@
           <t>Selenium Web Geo-IP lookup renders #191</t>
         </is>
       </c>
-      <c r="D192" t="n">
-        <v>0.73</v>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
@@ -4853,8 +5235,10 @@
           <t>Selenium Web Timeline filter applied #192</t>
         </is>
       </c>
-      <c r="D193" t="n">
-        <v>1.29</v>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
@@ -4876,8 +5260,10 @@
           <t>Selenium Web IOC search bar functional #193</t>
         </is>
       </c>
-      <c r="D194" t="n">
-        <v>1.31</v>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
@@ -4899,8 +5285,10 @@
           <t>Selenium Web IOC detail panel opens #194</t>
         </is>
       </c>
-      <c r="D195" t="n">
-        <v>1.1</v>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
@@ -4922,8 +5310,10 @@
           <t>Selenium Web IOC tag saved #195</t>
         </is>
       </c>
-      <c r="D196" t="n">
-        <v>0.41</v>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
@@ -4945,8 +5335,10 @@
           <t>Selenium Web CVE feed loads #196</t>
         </is>
       </c>
-      <c r="D197" t="n">
-        <v>0.71</v>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
@@ -4968,8 +5360,10 @@
           <t>Selenium Web STIX indicator displays #197</t>
         </is>
       </c>
-      <c r="D198" t="n">
-        <v>0.43</v>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
@@ -4991,8 +5385,10 @@
           <t>Selenium Web Export IOC CSV #198</t>
         </is>
       </c>
-      <c r="D199" t="n">
-        <v>0.79</v>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
@@ -5014,8 +5410,10 @@
           <t>Selenium Web Geo-IP lookup renders #199</t>
         </is>
       </c>
-      <c r="D200" t="n">
-        <v>1.72</v>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
@@ -5037,8 +5435,10 @@
           <t>Selenium Web Timeline filter applied #200</t>
         </is>
       </c>
-      <c r="D201" t="n">
-        <v>1.34</v>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
@@ -5060,8 +5460,10 @@
           <t>Selenium Web Generate PDF report #201</t>
         </is>
       </c>
-      <c r="D202" t="n">
-        <v>0.51</v>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
@@ -5083,8 +5485,10 @@
           <t>Selenium Web Download CSV export #202</t>
         </is>
       </c>
-      <c r="D203" t="n">
-        <v>0.42</v>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
@@ -5106,8 +5510,10 @@
           <t>Selenium Web Compliance checklist visible #203</t>
         </is>
       </c>
-      <c r="D204" t="n">
-        <v>0.61</v>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
@@ -5129,8 +5535,10 @@
           <t>Selenium Web Audit log table loads #204</t>
         </is>
       </c>
-      <c r="D205" t="n">
-        <v>1.22</v>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
@@ -5152,8 +5560,10 @@
           <t>Selenium Web Filter log by date #205</t>
         </is>
       </c>
-      <c r="D206" t="n">
-        <v>1.61</v>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
@@ -5175,8 +5585,10 @@
           <t>Selenium Web Search log by user #206</t>
         </is>
       </c>
-      <c r="D207" t="n">
-        <v>0.35</v>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
@@ -5198,8 +5610,10 @@
           <t>Selenium Web Log entry detail modal #207</t>
         </is>
       </c>
-      <c r="D208" t="n">
-        <v>0.68</v>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
@@ -5221,8 +5635,10 @@
           <t>Selenium Web Print preview opens #208</t>
         </is>
       </c>
-      <c r="D209" t="n">
-        <v>1.41</v>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
@@ -5244,8 +5660,10 @@
           <t>Selenium Web Generate PDF report #209</t>
         </is>
       </c>
-      <c r="D210" t="n">
-        <v>0.47</v>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
@@ -5267,8 +5685,10 @@
           <t>Selenium Web Download CSV export #210</t>
         </is>
       </c>
-      <c r="D211" t="n">
-        <v>1.29</v>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
@@ -5290,8 +5710,10 @@
           <t>Selenium Web Compliance checklist visible #211</t>
         </is>
       </c>
-      <c r="D212" t="n">
-        <v>1.61</v>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
@@ -5313,8 +5735,10 @@
           <t>Selenium Web Audit log table loads #212</t>
         </is>
       </c>
-      <c r="D213" t="n">
-        <v>1.59</v>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
@@ -5336,8 +5760,10 @@
           <t>Selenium Web Filter log by date #213</t>
         </is>
       </c>
-      <c r="D214" t="n">
-        <v>1.47</v>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
@@ -5359,8 +5785,10 @@
           <t>Selenium Web Search log by user #214</t>
         </is>
       </c>
-      <c r="D215" t="n">
-        <v>1.37</v>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
@@ -5382,8 +5810,10 @@
           <t>Selenium Web Log entry detail modal #215</t>
         </is>
       </c>
-      <c r="D216" t="n">
-        <v>1.27</v>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
@@ -5405,8 +5835,10 @@
           <t>Selenium Web Print preview opens #216</t>
         </is>
       </c>
-      <c r="D217" t="n">
-        <v>1.11</v>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
@@ -5428,8 +5860,10 @@
           <t>Selenium Web Generate PDF report #217</t>
         </is>
       </c>
-      <c r="D218" t="n">
-        <v>1.33</v>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
@@ -5451,8 +5885,10 @@
           <t>Selenium Web Download CSV export #218</t>
         </is>
       </c>
-      <c r="D219" t="n">
-        <v>0.34</v>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
@@ -5474,8 +5910,10 @@
           <t>Selenium Web Compliance checklist visible #219</t>
         </is>
       </c>
-      <c r="D220" t="n">
-        <v>1.25</v>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
@@ -5497,8 +5935,10 @@
           <t>Selenium Web Audit log table loads #220</t>
         </is>
       </c>
-      <c r="D221" t="n">
-        <v>0.6</v>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
@@ -5520,8 +5960,10 @@
           <t>Selenium Web Filter log by date #221</t>
         </is>
       </c>
-      <c r="D222" t="n">
-        <v>0.39</v>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
@@ -5543,8 +5985,10 @@
           <t>Selenium Web Search log by user #222</t>
         </is>
       </c>
-      <c r="D223" t="n">
-        <v>0.89</v>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
@@ -5566,8 +6010,10 @@
           <t>Selenium Web Log entry detail modal #223</t>
         </is>
       </c>
-      <c r="D224" t="n">
-        <v>0.72</v>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
@@ -5589,8 +6035,10 @@
           <t>Selenium Web Print preview opens #224</t>
         </is>
       </c>
-      <c r="D225" t="n">
-        <v>1.15</v>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
@@ -5612,8 +6060,10 @@
           <t>Selenium Web Generate PDF report #225</t>
         </is>
       </c>
-      <c r="D226" t="n">
-        <v>1.73</v>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
@@ -5635,8 +6085,10 @@
           <t>Selenium Web Download CSV export #226</t>
         </is>
       </c>
-      <c r="D227" t="n">
-        <v>0.32</v>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
@@ -5658,8 +6110,10 @@
           <t>Selenium Web Compliance checklist visible #227</t>
         </is>
       </c>
-      <c r="D228" t="n">
-        <v>0.16</v>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
@@ -5681,8 +6135,10 @@
           <t>Selenium Web Audit log table loads #228</t>
         </is>
       </c>
-      <c r="D229" t="n">
-        <v>1.68</v>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
@@ -5704,8 +6160,10 @@
           <t>Selenium Web Filter log by date #229</t>
         </is>
       </c>
-      <c r="D230" t="n">
-        <v>1.14</v>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
@@ -5727,8 +6185,10 @@
           <t>Selenium Web Search log by user #230</t>
         </is>
       </c>
-      <c r="D231" t="n">
-        <v>0.92</v>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
@@ -5750,8 +6210,10 @@
           <t>Selenium Web Log entry detail modal #231</t>
         </is>
       </c>
-      <c r="D232" t="n">
-        <v>0.98</v>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
@@ -5773,8 +6235,10 @@
           <t>Selenium Web Print preview opens #232</t>
         </is>
       </c>
-      <c r="D233" t="n">
-        <v>0.27</v>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
@@ -5796,8 +6260,10 @@
           <t>Selenium Web Generate PDF report #233</t>
         </is>
       </c>
-      <c r="D234" t="n">
-        <v>0.19</v>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
@@ -5819,8 +6285,10 @@
           <t>Selenium Web Download CSV export #234</t>
         </is>
       </c>
-      <c r="D235" t="n">
-        <v>0.21</v>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
@@ -5842,8 +6310,10 @@
           <t>Selenium Web Compliance checklist visible #235</t>
         </is>
       </c>
-      <c r="D236" t="n">
-        <v>1.62</v>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
@@ -5865,8 +6335,10 @@
           <t>Selenium Web Audit log table loads #236</t>
         </is>
       </c>
-      <c r="D237" t="n">
-        <v>0.21</v>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
@@ -5888,8 +6360,10 @@
           <t>Selenium Web Filter log by date #237</t>
         </is>
       </c>
-      <c r="D238" t="n">
-        <v>0.45</v>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
@@ -5911,8 +6385,10 @@
           <t>Selenium Web Search log by user #238</t>
         </is>
       </c>
-      <c r="D239" t="n">
-        <v>1.01</v>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
@@ -5934,8 +6410,10 @@
           <t>Selenium Web Log entry detail modal #239</t>
         </is>
       </c>
-      <c r="D240" t="n">
-        <v>0.46</v>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
@@ -5957,8 +6435,10 @@
           <t>Selenium Web Print preview opens #240</t>
         </is>
       </c>
-      <c r="D241" t="n">
-        <v>0.17</v>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
@@ -5980,8 +6460,10 @@
           <t>Selenium Web Dark theme toggle #241</t>
         </is>
       </c>
-      <c r="D242" t="n">
-        <v>0.9</v>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
@@ -6003,8 +6485,10 @@
           <t>Selenium Web Notification prefs saved #242</t>
         </is>
       </c>
-      <c r="D243" t="n">
-        <v>1.11</v>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
@@ -6026,8 +6510,10 @@
           <t>Selenium Web API server URL updated #243</t>
         </is>
       </c>
-      <c r="D244" t="n">
-        <v>0.99</v>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
@@ -6049,8 +6535,10 @@
           <t>Selenium Web Language preference stored #244</t>
         </is>
       </c>
-      <c r="D245" t="n">
-        <v>1.32</v>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
@@ -6072,8 +6560,10 @@
           <t>Selenium Web Session timeout config #245</t>
         </is>
       </c>
-      <c r="D246" t="n">
-        <v>0.52</v>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
@@ -6095,8 +6585,10 @@
           <t>Selenium Web SMTP test email sent #246</t>
         </is>
       </c>
-      <c r="D247" t="n">
-        <v>1.39</v>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
@@ -6118,8 +6610,10 @@
           <t>Selenium Web Backup config download #247</t>
         </is>
       </c>
-      <c r="D248" t="n">
-        <v>1.34</v>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
@@ -6141,8 +6635,10 @@
           <t>Selenium Web Restore config upload #248</t>
         </is>
       </c>
-      <c r="D249" t="n">
-        <v>0.68</v>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
@@ -6164,8 +6660,10 @@
           <t>Selenium Web Dark theme toggle #249</t>
         </is>
       </c>
-      <c r="D250" t="n">
-        <v>1.17</v>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
@@ -6187,8 +6685,10 @@
           <t>Selenium Web Notification prefs saved #250</t>
         </is>
       </c>
-      <c r="D251" t="n">
-        <v>1.32</v>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
@@ -6210,8 +6710,10 @@
           <t>Selenium Web API server URL updated #251</t>
         </is>
       </c>
-      <c r="D252" t="n">
-        <v>1.66</v>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
@@ -6233,8 +6735,10 @@
           <t>Selenium Web Language preference stored #252</t>
         </is>
       </c>
-      <c r="D253" t="n">
-        <v>1.31</v>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
@@ -6256,8 +6760,10 @@
           <t>Selenium Web Session timeout config #253</t>
         </is>
       </c>
-      <c r="D254" t="n">
-        <v>0.8100000000000001</v>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
@@ -6279,8 +6785,10 @@
           <t>Selenium Web SMTP test email sent #254</t>
         </is>
       </c>
-      <c r="D255" t="n">
-        <v>0.11</v>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
@@ -6302,8 +6810,10 @@
           <t>Selenium Web Backup config download #255</t>
         </is>
       </c>
-      <c r="D256" t="n">
-        <v>1.67</v>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
@@ -6325,8 +6835,10 @@
           <t>Selenium Web Restore config upload #256</t>
         </is>
       </c>
-      <c r="D257" t="n">
-        <v>0.58</v>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
@@ -6348,8 +6860,10 @@
           <t>Selenium Web Dark theme toggle #257</t>
         </is>
       </c>
-      <c r="D258" t="n">
-        <v>1.79</v>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
@@ -6371,8 +6885,10 @@
           <t>Selenium Web Notification prefs saved #258</t>
         </is>
       </c>
-      <c r="D259" t="n">
-        <v>1.58</v>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
@@ -6394,8 +6910,10 @@
           <t>Selenium Web API server URL updated #259</t>
         </is>
       </c>
-      <c r="D260" t="n">
-        <v>1.39</v>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
@@ -6417,8 +6935,10 @@
           <t>Selenium Web Language preference stored #260</t>
         </is>
       </c>
-      <c r="D261" t="n">
-        <v>0.98</v>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
@@ -6440,8 +6960,10 @@
           <t>Selenium Web Session timeout config #261</t>
         </is>
       </c>
-      <c r="D262" t="n">
-        <v>0.83</v>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
@@ -6463,8 +6985,10 @@
           <t>Selenium Web SMTP test email sent #262</t>
         </is>
       </c>
-      <c r="D263" t="n">
-        <v>1.39</v>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
@@ -6486,8 +7010,10 @@
           <t>Selenium Web Backup config download #263</t>
         </is>
       </c>
-      <c r="D264" t="n">
-        <v>0.92</v>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
@@ -6509,8 +7035,10 @@
           <t>Selenium Web Restore config upload #264</t>
         </is>
       </c>
-      <c r="D265" t="n">
-        <v>0.29</v>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
@@ -6532,8 +7060,10 @@
           <t>Selenium Web Dark theme toggle #265</t>
         </is>
       </c>
-      <c r="D266" t="n">
-        <v>0.6899999999999999</v>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
@@ -6555,8 +7085,10 @@
           <t>Selenium Web Notification prefs saved #266</t>
         </is>
       </c>
-      <c r="D267" t="n">
-        <v>1.41</v>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
@@ -6578,8 +7110,10 @@
           <t>Selenium Web API server URL updated #267</t>
         </is>
       </c>
-      <c r="D268" t="n">
-        <v>1.46</v>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
@@ -6601,8 +7135,10 @@
           <t>Selenium Web Language preference stored #268</t>
         </is>
       </c>
-      <c r="D269" t="n">
-        <v>0.97</v>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
@@ -6624,8 +7160,10 @@
           <t>Selenium Web Session timeout config #269</t>
         </is>
       </c>
-      <c r="D270" t="n">
-        <v>1.4</v>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
@@ -6647,8 +7185,10 @@
           <t>Selenium Web SMTP test email sent #270</t>
         </is>
       </c>
-      <c r="D271" t="n">
-        <v>0.1</v>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
@@ -6670,8 +7210,10 @@
           <t>Selenium Web Backup config download #271</t>
         </is>
       </c>
-      <c r="D272" t="n">
-        <v>1.21</v>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
@@ -6693,8 +7235,10 @@
           <t>Selenium Web Restore config upload #272</t>
         </is>
       </c>
-      <c r="D273" t="n">
-        <v>0.7</v>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
@@ -6716,8 +7260,10 @@
           <t>Selenium Web Dark theme toggle #273</t>
         </is>
       </c>
-      <c r="D274" t="n">
-        <v>0.95</v>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
@@ -6739,8 +7285,10 @@
           <t>Selenium Web Notification prefs saved #274</t>
         </is>
       </c>
-      <c r="D275" t="n">
-        <v>0.96</v>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
@@ -6762,8 +7310,10 @@
           <t>Selenium Web API server URL updated #275</t>
         </is>
       </c>
-      <c r="D276" t="n">
-        <v>0.36</v>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
@@ -6785,8 +7335,10 @@
           <t>Selenium Web Language preference stored #276</t>
         </is>
       </c>
-      <c r="D277" t="n">
-        <v>0.67</v>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
@@ -6808,8 +7360,10 @@
           <t>Selenium Web Session timeout config #277</t>
         </is>
       </c>
-      <c r="D278" t="n">
-        <v>1.43</v>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
@@ -6831,8 +7385,10 @@
           <t>Selenium Web SMTP test email sent #278</t>
         </is>
       </c>
-      <c r="D279" t="n">
-        <v>1.79</v>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
@@ -6854,8 +7410,10 @@
           <t>Selenium Web Backup config download #279</t>
         </is>
       </c>
-      <c r="D280" t="n">
-        <v>1.78</v>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
@@ -6877,10 +7435,712 @@
           <t>Selenium Web Restore config upload #280</t>
         </is>
       </c>
-      <c r="D281" t="n">
-        <v>0.68</v>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E281" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>281</v>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>UI / E2E</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>TC_SELENIUM_0281 - SentinelX Web Portal Validation Flow</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>282</v>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>UI / E2E</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>TC_SELENIUM_0282 - SentinelX Web Portal Validation Flow</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>283</v>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>UI / E2E</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>TC_SELENIUM_0283 - SentinelX Web Portal Validation Flow</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>284</v>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>UI / E2E</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>TC_SELENIUM_0284 - SentinelX Web Portal Validation Flow</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>285</v>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>UI / E2E</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>TC_SELENIUM_0285 - SentinelX Web Portal Validation Flow</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>286</v>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>UI / E2E</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>TC_SELENIUM_0286 - SentinelX Web Portal Validation Flow</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
+        <v>287</v>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>UI / E2E</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>TC_SELENIUM_0287 - SentinelX Web Portal Validation Flow</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>288</v>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>UI / E2E</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>TC_SELENIUM_0288 - SentinelX Web Portal Validation Flow</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="n">
+        <v>289</v>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>UI / E2E</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>TC_SELENIUM_0289 - SentinelX Web Portal Validation Flow</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="n">
+        <v>290</v>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>UI / E2E</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>TC_SELENIUM_0290 - SentinelX Web Portal Validation Flow</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="n">
+        <v>291</v>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>UI / E2E</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>TC_SELENIUM_0291 - SentinelX Web Portal Validation Flow</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="n">
+        <v>292</v>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>UI / E2E</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>TC_SELENIUM_0292 - SentinelX Web Portal Validation Flow</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="n">
+        <v>293</v>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>UI / E2E</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>TC_SELENIUM_0293 - SentinelX Web Portal Validation Flow</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="n">
+        <v>294</v>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>UI / E2E</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>TC_SELENIUM_0294 - SentinelX Web Portal Validation Flow</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="n">
+        <v>295</v>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>UI / E2E</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>TC_SELENIUM_0295 - SentinelX Web Portal Validation Flow</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="n">
+        <v>296</v>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>UI / E2E</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>TC_SELENIUM_0296 - SentinelX Web Portal Validation Flow</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="n">
+        <v>297</v>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>UI / E2E</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>TC_SELENIUM_0297 - SentinelX Web Portal Validation Flow</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="n">
+        <v>298</v>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>UI / E2E</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>TC_SELENIUM_0298 - SentinelX Web Portal Validation Flow</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="n">
+        <v>299</v>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>UI / E2E</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>TC_SELENIUM_0299 - SentinelX Web Portal Validation Flow</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="n">
+        <v>300</v>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>UI / E2E</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>TC_SELENIUM_0300 - SentinelX Web Portal Validation Flow</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="n">
+        <v>301</v>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>UI / E2E</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>TC_SELENIUM_0301 - SentinelX Web Portal Validation Flow</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="n">
+        <v>302</v>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>UI / E2E</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>TC_SELENIUM_0302 - SentinelX Web Portal Validation Flow</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="n">
+        <v>303</v>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>UI / E2E</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>TC_SELENIUM_0303 - SentinelX Web Portal Validation Flow</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="n">
+        <v>304</v>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>UI / E2E</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>TC_SELENIUM_0304 - SentinelX Web Portal Validation Flow</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="n">
+        <v>305</v>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>UI / E2E</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>TC_SELENIUM_0305 - SentinelX Web Portal Validation Flow</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="n">
+        <v>306</v>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>UI / E2E</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>TC_SELENIUM_0306 - SentinelX Web Portal Validation Flow</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="n">
+        <v>307</v>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>UI / E2E</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>TC_SELENIUM_0307 - SentinelX Web Portal Validation Flow</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="n">
+        <v>308</v>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>UI / E2E</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>TC_SELENIUM_0308 - SentinelX Web Portal Validation Flow</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="n">
+        <v>309</v>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>UI / E2E</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>TC_SELENIUM_0309 - SentinelX Web Portal Validation Flow</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="n">
+        <v>310</v>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>UI / E2E</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>TC_SELENIUM_0310 - SentinelX Web Portal Validation Flow</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="n">
+        <v>311</v>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>UI / E2E</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>TC_SELENIUM_0311 - SentinelX Web Portal Validation Flow</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="n">
+        <v>312</v>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>UI / E2E</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>TC_SELENIUM_0312 - SentinelX Web Portal Validation Flow</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="n">
+        <v>313</v>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>UI / E2E</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>TC_SELENIUM_0313 - SentinelX Web Portal Validation Flow</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="n">
+        <v>314</v>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>UI / E2E</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>TC_SELENIUM_0314 - SentinelX Web Portal Validation Flow</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="n">
+        <v>315</v>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>UI / E2E</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>TC_SELENIUM_0315 - SentinelX Web Portal Validation Flow</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
         <is>
           <t>PASSED</t>
         </is>
